--- a/Result/profitability/2546.xlsx
+++ b/Result/profitability/2546.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>2.03375</v>
+        <v>2.73375</v>
       </c>
       <c r="N2" t="n">
-        <v>8.58625</v>
+        <v>9.754999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>1.83375</v>
+        <v>2.37125</v>
       </c>
       <c r="N3" t="n">
-        <v>8.174999999999999</v>
+        <v>8.870000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>1.455</v>
+        <v>2.19625</v>
       </c>
       <c r="N4" t="n">
-        <v>7.49375</v>
+        <v>8.81</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.29625</v>
+        <v>1.96125</v>
       </c>
       <c r="N5" t="n">
-        <v>7.130000000000001</v>
+        <v>8.43375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.10375</v>
+        <v>1.645</v>
       </c>
       <c r="N6" t="n">
-        <v>6.98125</v>
+        <v>8.251250000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>1.19</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8612500000000001</v>
+        <v>1.4275</v>
       </c>
       <c r="N7" t="n">
-        <v>6.88</v>
+        <v>7.99625</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5775</v>
+        <v>1.33125</v>
       </c>
       <c r="N8" t="n">
-        <v>6.47</v>
+        <v>7.81125</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>0.57625</v>
+        <v>0.5762499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>7.15625</v>
@@ -1645,7 +1645,7 @@
         <v>1.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7025000000000001</v>
+        <v>0.7025</v>
       </c>
       <c r="N10" t="n">
         <v>7.936249999999999</v>
@@ -1899,7 +1899,7 @@
         <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9312499999999999</v>
+        <v>0.93125</v>
       </c>
       <c r="N12" t="n">
         <v>7.89875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6982</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5691</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1291</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1143</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>84</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1227</v>
+      </c>
+      <c r="K75" t="n">
+        <v>974</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.955</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.27875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.216783216783217</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.382731958762887</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.485981308411215</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.294044665012406</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
